--- a/PAMF_DIG F2 - monthly2026-07-22.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-22.xlsx
@@ -2239,7 +2239,7 @@
         <v>0.09</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>0.09</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>0.09</v>
       </c>
       <c r="N93" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>0.09</v>
       </c>
       <c r="N98" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>0.09</v>
       </c>
       <c r="N128" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>0.09</v>
       </c>
       <c r="N131" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>0.09</v>
       </c>
       <c r="N140" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>0.09</v>
       </c>
       <c r="N154" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>0.09</v>
       </c>
       <c r="N166" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>0.09</v>
       </c>
       <c r="N179" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>0.09</v>
       </c>
       <c r="N186" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>0.09</v>
       </c>
       <c r="N187" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>0.09</v>
       </c>
       <c r="N188" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>0.09</v>
       </c>
       <c r="N203" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>0.09</v>
       </c>
       <c r="N204" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>0.09</v>
       </c>
       <c r="N225" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>0.09</v>
       </c>
       <c r="N228" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>0.09</v>
       </c>
       <c r="N240" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>0.09</v>
       </c>
       <c r="N241" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O241" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>0.09</v>
       </c>
       <c r="N253" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O253" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>0.09</v>
       </c>
       <c r="N293" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O293" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>0.09</v>
       </c>
       <c r="N316" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O316" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>0.09</v>
       </c>
       <c r="N363" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O363" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>0.09</v>
       </c>
       <c r="N371" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O371" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>0.09</v>
       </c>
       <c r="N372" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O372" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>0.09</v>
       </c>
       <c r="N375" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O375" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>0.09</v>
       </c>
       <c r="N403" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O403" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>0.09</v>
       </c>
       <c r="N407" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O407" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-22.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-22.xlsx
@@ -560,7 +560,7 @@
         <v>0.09</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         <v>0.09</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>0.09</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>0.09</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>0.09</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>0.09</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>0.09</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>0.09</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>0.09</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>0.09</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>0.09</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>0.09</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>0.09</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>0.09</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>0.09</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>0.09</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>0.09</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>0.09</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>0.09</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>0.09</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>0.09</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>0.09</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>0.09</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>0.09</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>0.09</v>
       </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>0.09</v>
       </c>
       <c r="N36" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>0.09</v>
       </c>
       <c r="N37" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>0.09</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>0.09</v>
       </c>
       <c r="N39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>0.09</v>
       </c>
       <c r="N40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>0.09</v>
       </c>
       <c r="N41" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>0.09</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>0.09</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>0.09</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>0.09</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>0.09</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>0.09</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>0.09</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>0.09</v>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>0.09</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>0.09</v>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>0.09</v>
       </c>
       <c r="N52" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>0.09</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>0.09</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>0.09</v>
       </c>
       <c r="N55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>0.09</v>
       </c>
       <c r="N58" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>0.09</v>
       </c>
       <c r="N59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>0.09</v>
       </c>
       <c r="N60" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>0.09</v>
       </c>
       <c r="N61" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>0.09</v>
       </c>
       <c r="N62" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>0.09</v>
       </c>
       <c r="N64" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>0.09</v>
       </c>
       <c r="N65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>0.09</v>
       </c>
       <c r="N66" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>0.09</v>
       </c>
       <c r="N67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>0.09</v>
       </c>
       <c r="N68" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>0.09</v>
       </c>
       <c r="N71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>0.09</v>
       </c>
       <c r="N73" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>0.09</v>
       </c>
       <c r="N74" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>0.09</v>
       </c>
       <c r="N75" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>0.09</v>
       </c>
       <c r="N76" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>0.09</v>
       </c>
       <c r="N77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>0.09</v>
       </c>
       <c r="N78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>0.09</v>
       </c>
       <c r="N79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>0.09</v>
       </c>
       <c r="N81" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>0.09</v>
       </c>
       <c r="N82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>0.09</v>
       </c>
       <c r="N83" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>0.09</v>
       </c>
       <c r="N85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>0.09</v>
       </c>
       <c r="N87" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>0.09</v>
       </c>
       <c r="N89" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>0.09</v>
       </c>
       <c r="N90" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>0.09</v>
       </c>
       <c r="N91" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>0.09</v>
       </c>
       <c r="N92" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>0.09</v>
       </c>
       <c r="N94" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>0.09</v>
       </c>
       <c r="N95" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>0.09</v>
       </c>
       <c r="N96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>0.09</v>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>0.09</v>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>0.09</v>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>0.09</v>
       </c>
       <c r="N101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>0.09</v>
       </c>
       <c r="N102" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>0.09</v>
       </c>
       <c r="N103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>0.09</v>
       </c>
       <c r="N104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>0.09</v>
       </c>
       <c r="N105" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>0.09</v>
       </c>
       <c r="N106" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>0.09</v>
       </c>
       <c r="N107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>0.09</v>
       </c>
       <c r="N108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>0.09</v>
       </c>
       <c r="N109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>0.09</v>
       </c>
       <c r="N110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>0.09</v>
       </c>
       <c r="N111" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>0.09</v>
       </c>
       <c r="N112" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>0.09</v>
       </c>
       <c r="N113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>0.09</v>
       </c>
       <c r="N114" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>0.09</v>
       </c>
       <c r="N115" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>0.09</v>
       </c>
       <c r="N116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>0.09</v>
       </c>
       <c r="N117" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>0.09</v>
       </c>
       <c r="N118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>0.09</v>
       </c>
       <c r="N122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>0.09</v>
       </c>
       <c r="N123" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>0.09</v>
       </c>
       <c r="N124" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>0.09</v>
       </c>
       <c r="N125" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>0.09</v>
       </c>
       <c r="N126" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>0.09</v>
       </c>
       <c r="N127" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>0.09</v>
       </c>
       <c r="N130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>0.09</v>
       </c>
       <c r="N132" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>0.09</v>
       </c>
       <c r="N133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>0.09</v>
       </c>
       <c r="N134" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>0.09</v>
       </c>
       <c r="N135" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>0.09</v>
       </c>
       <c r="N136" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>0.09</v>
       </c>
       <c r="N138" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>0.09</v>
       </c>
       <c r="N139" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>0.09</v>
       </c>
       <c r="N141" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>0.09</v>
       </c>
       <c r="N142" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>0.09</v>
       </c>
       <c r="N143" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>0.09</v>
       </c>
       <c r="N144" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>0.09</v>
       </c>
       <c r="N145" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>0.09</v>
       </c>
       <c r="N148" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>0.09</v>
       </c>
       <c r="N149" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>0.09</v>
       </c>
       <c r="N150" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>0.09</v>
       </c>
       <c r="N151" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>0.09</v>
       </c>
       <c r="N152" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>0.09</v>
       </c>
       <c r="N153" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>0.09</v>
       </c>
       <c r="N155" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>0.09</v>
       </c>
       <c r="N156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>0.09</v>
       </c>
       <c r="N157" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>0.09</v>
       </c>
       <c r="N158" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>0.09</v>
       </c>
       <c r="N160" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>0.09</v>
       </c>
       <c r="N161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>0.09</v>
       </c>
       <c r="N162" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>0.09</v>
       </c>
       <c r="N164" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>0.09</v>
       </c>
       <c r="N165" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>0.09</v>
       </c>
       <c r="N167" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>0.09</v>
       </c>
       <c r="N168" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>0.09</v>
       </c>
       <c r="N169" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>0.09</v>
       </c>
       <c r="N170" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>0.09</v>
       </c>
       <c r="N171" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>0.09</v>
       </c>
       <c r="N172" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>0.09</v>
       </c>
       <c r="N174" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>0.09</v>
       </c>
       <c r="N175" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>0.09</v>
       </c>
       <c r="N177" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>0.09</v>
       </c>
       <c r="N178" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>0.09</v>
       </c>
       <c r="N180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>0.09</v>
       </c>
       <c r="N181" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>0.09</v>
       </c>
       <c r="N183" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>0.09</v>
       </c>
       <c r="N184" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>0.09</v>
       </c>
       <c r="N191" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>0.09</v>
       </c>
       <c r="N194" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>0.09</v>
       </c>
       <c r="N195" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>0.09</v>
       </c>
       <c r="N196" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>0.09</v>
       </c>
       <c r="N197" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>0.09</v>
       </c>
       <c r="N199" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>0.09</v>
       </c>
       <c r="N201" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>0.09</v>
       </c>
       <c r="N202" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>0.09</v>
       </c>
       <c r="N206" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>0.09</v>
       </c>
       <c r="N208" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>0.09</v>
       </c>
       <c r="N209" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>0.09</v>
       </c>
       <c r="N210" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>0.09</v>
       </c>
       <c r="N211" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>0.09</v>
       </c>
       <c r="N212" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>0.09</v>
       </c>
       <c r="N213" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>0.09</v>
       </c>
       <c r="N214" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O214" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>0.09</v>
       </c>
       <c r="N215" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O215" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>0.09</v>
       </c>
       <c r="N217" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>0.09</v>
       </c>
       <c r="N218" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>0.09</v>
       </c>
       <c r="N219" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>0.09</v>
       </c>
       <c r="N221" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>0.09</v>
       </c>
       <c r="N222" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>0.09</v>
       </c>
       <c r="N223" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>0.09</v>
       </c>
       <c r="N224" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>0.09</v>
       </c>
       <c r="N226" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>0.09</v>
       </c>
       <c r="N227" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>0.09</v>
       </c>
       <c r="N229" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>0.09</v>
       </c>
       <c r="N230" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>0.09</v>
       </c>
       <c r="N231" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>0.09</v>
       </c>
       <c r="N232" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>0.09</v>
       </c>
       <c r="N235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>0.09</v>
       </c>
       <c r="N236" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>0.09</v>
       </c>
       <c r="N237" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O237" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>0.09</v>
       </c>
       <c r="N238" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O238" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>0.09</v>
       </c>
       <c r="N239" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O239" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>0.09</v>
       </c>
       <c r="N242" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O242" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>0.09</v>
       </c>
       <c r="N243" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O243" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>0.09</v>
       </c>
       <c r="N246" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>0.09</v>
       </c>
       <c r="N248" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>0.09</v>
       </c>
       <c r="N249" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>0.09</v>
       </c>
       <c r="N250" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O250" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>0.09</v>
       </c>
       <c r="N251" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>0.09</v>
       </c>
       <c r="N252" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O252" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>0.09</v>
       </c>
       <c r="N254" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>0.09</v>
       </c>
       <c r="N257" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>0.09</v>
       </c>
       <c r="N259" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>0.09</v>
       </c>
       <c r="N260" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>0.09</v>
       </c>
       <c r="N261" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>0.09</v>
       </c>
       <c r="N262" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O262" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>0.09</v>
       </c>
       <c r="N263" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O263" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>0.09</v>
       </c>
       <c r="N264" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O264" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>0.09</v>
       </c>
       <c r="N265" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O265" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>0.09</v>
       </c>
       <c r="N266" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O266" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>0.09</v>
       </c>
       <c r="N267" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O267" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>0.09</v>
       </c>
       <c r="N268" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O268" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>0.09</v>
       </c>
       <c r="N269" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O269" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>0.09</v>
       </c>
       <c r="N271" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O271" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>0.09</v>
       </c>
       <c r="N273" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O273" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>0.09</v>
       </c>
       <c r="N274" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>0.09</v>
       </c>
       <c r="N275" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O275" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>0.09</v>
       </c>
       <c r="N276" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O276" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>0.09</v>
       </c>
       <c r="N277" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O277" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>0.09</v>
       </c>
       <c r="N278" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O278" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>0.09</v>
       </c>
       <c r="N279" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O279" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>0.09</v>
       </c>
       <c r="N280" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>0.09</v>
       </c>
       <c r="N281" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O281" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>0.09</v>
       </c>
       <c r="N284" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O284" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>0.09</v>
       </c>
       <c r="N286" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O286" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>0.09</v>
       </c>
       <c r="N287" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O287" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>0.09</v>
       </c>
       <c r="N288" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O288" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>0.09</v>
       </c>
       <c r="N289" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O289" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>0.09</v>
       </c>
       <c r="N290" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O290" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>0.09</v>
       </c>
       <c r="N291" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O291" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>0.09</v>
       </c>
       <c r="N294" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O294" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>0.09</v>
       </c>
       <c r="N295" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O295" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>0.09</v>
       </c>
       <c r="N296" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O296" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>0.09</v>
       </c>
       <c r="N297" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O297" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>0.09</v>
       </c>
       <c r="N298" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O298" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>0.09</v>
       </c>
       <c r="N299" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>0.09</v>
       </c>
       <c r="N300" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O300" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>0.09</v>
       </c>
       <c r="N301" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O301" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>0.09</v>
       </c>
       <c r="N302" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O302" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>0.09</v>
       </c>
       <c r="N303" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O303" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>0.09</v>
       </c>
       <c r="N304" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O304" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>0.09</v>
       </c>
       <c r="N305" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O305" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>0.09</v>
       </c>
       <c r="N306" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O306" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>0.09</v>
       </c>
       <c r="N307" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O307" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>0.09</v>
       </c>
       <c r="N308" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O308" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>0.09</v>
       </c>
       <c r="N309" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>0.09</v>
       </c>
       <c r="N311" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O311" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>0.09</v>
       </c>
       <c r="N312" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O312" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>0.09</v>
       </c>
       <c r="N313" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O313" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>0.09</v>
       </c>
       <c r="N314" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>0.09</v>
       </c>
       <c r="N315" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>0.09</v>
       </c>
       <c r="N317" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>0.09</v>
       </c>
       <c r="N318" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>0.09</v>
       </c>
       <c r="N319" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>0.09</v>
       </c>
       <c r="N320" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>0.09</v>
       </c>
       <c r="N323" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O323" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>0.09</v>
       </c>
       <c r="N324" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O324" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>0.09</v>
       </c>
       <c r="N326" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O326" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>0.09</v>
       </c>
       <c r="N327" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O327" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>0.09</v>
       </c>
       <c r="N328" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O328" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>0.09</v>
       </c>
       <c r="N329" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O329" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>0.09</v>
       </c>
       <c r="N330" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O330" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>0.09</v>
       </c>
       <c r="N332" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O332" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>0.09</v>
       </c>
       <c r="N333" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O333" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>0.09</v>
       </c>
       <c r="N334" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O334" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>0.09</v>
       </c>
       <c r="N335" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O335" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>0.09</v>
       </c>
       <c r="N336" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O336" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>0.09</v>
       </c>
       <c r="N337" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O337" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>0.09</v>
       </c>
       <c r="N338" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O338" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>0.09</v>
       </c>
       <c r="N340" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O340" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>0.09</v>
       </c>
       <c r="N341" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O341" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>0.09</v>
       </c>
       <c r="N343" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O343" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>0.09</v>
       </c>
       <c r="N344" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O344" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>0.09</v>
       </c>
       <c r="N346" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O346" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>0.09</v>
       </c>
       <c r="N347" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O347" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>0.09</v>
       </c>
       <c r="N348" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O348" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>0.09</v>
       </c>
       <c r="N351" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O351" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>0.09</v>
       </c>
       <c r="N352" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O352" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>0.09</v>
       </c>
       <c r="N353" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O353" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>0.09</v>
       </c>
       <c r="N354" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O354" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>0.09</v>
       </c>
       <c r="N355" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O355" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>0.09</v>
       </c>
       <c r="N356" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O356" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>0.09</v>
       </c>
       <c r="N357" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O357" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>0.09</v>
       </c>
       <c r="N358" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O358" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>0.09</v>
       </c>
       <c r="N359" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O359" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>0.09</v>
       </c>
       <c r="N360" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O360" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>0.09</v>
       </c>
       <c r="N362" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O362" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>0.09</v>
       </c>
       <c r="N364" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O364" t="inlineStr">
         <is>
@@ -27059,7 +27059,7 @@
         <v>0.09</v>
       </c>
       <c r="N365" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O365" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>0.09</v>
       </c>
       <c r="N366" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O366" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>0.09</v>
       </c>
       <c r="N367" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O367" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>0.09</v>
       </c>
       <c r="N368" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O368" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>0.09</v>
       </c>
       <c r="N369" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O369" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>0.09</v>
       </c>
       <c r="N370" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O370" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>0.09</v>
       </c>
       <c r="N373" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O373" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>0.09</v>
       </c>
       <c r="N374" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O374" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>0.09</v>
       </c>
       <c r="N378" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O378" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>0.09</v>
       </c>
       <c r="N379" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O379" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>0.09</v>
       </c>
       <c r="N380" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O380" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>0.09</v>
       </c>
       <c r="N384" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O384" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>0.09</v>
       </c>
       <c r="N385" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O385" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>0.09</v>
       </c>
       <c r="N386" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O386" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>0.09</v>
       </c>
       <c r="N387" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O387" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>0.09</v>
       </c>
       <c r="N389" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O389" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>0.09</v>
       </c>
       <c r="N390" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O390" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>0.09</v>
       </c>
       <c r="N391" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O391" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>0.09</v>
       </c>
       <c r="N392" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O392" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>0.09</v>
       </c>
       <c r="N393" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O393" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>0.09</v>
       </c>
       <c r="N397" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O397" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>0.09</v>
       </c>
       <c r="N399" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O399" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>0.09</v>
       </c>
       <c r="N400" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O400" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>0.09</v>
       </c>
       <c r="N401" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O401" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>0.09</v>
       </c>
       <c r="N402" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O402" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>0.09</v>
       </c>
       <c r="N404" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O404" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>0.09</v>
       </c>
       <c r="N406" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O406" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>0.09</v>
       </c>
       <c r="N408" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O408" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>0.09</v>
       </c>
       <c r="N409" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O409" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>0.09</v>
       </c>
       <c r="N410" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O410" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>0.09</v>
       </c>
       <c r="N411" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O411" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>0.09</v>
       </c>
       <c r="N412" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O412" t="inlineStr">
         <is>
@@ -30563,7 +30563,7 @@
         <v>0.09</v>
       </c>
       <c r="N413" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O413" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>0.09</v>
       </c>
       <c r="N415" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O415" t="inlineStr">
         <is>
@@ -30855,7 +30855,7 @@
         <v>0.09</v>
       </c>
       <c r="N417" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O417" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>0.09</v>
       </c>
       <c r="N418" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O418" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>0.09</v>
       </c>
       <c r="N419" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O419" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>0.09</v>
       </c>
       <c r="N420" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O420" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>0.09</v>
       </c>
       <c r="N421" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O421" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>0.09</v>
       </c>
       <c r="N422" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O422" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>0.09</v>
       </c>
       <c r="N423" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O423" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>0.09</v>
       </c>
       <c r="N427" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O427" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>0.09</v>
       </c>
       <c r="N428" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O428" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>0.09</v>
       </c>
       <c r="N429" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O429" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>0.09</v>
       </c>
       <c r="N431" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O431" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>0.09</v>
       </c>
       <c r="N432" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O432" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         <v>0.09</v>
       </c>
       <c r="N433" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O433" t="inlineStr">
         <is>
@@ -32096,7 +32096,7 @@
         <v>0.09</v>
       </c>
       <c r="N434" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O434" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>0.09</v>
       </c>
       <c r="N435" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O435" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>0.09</v>
       </c>
       <c r="N436" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O436" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>0.09</v>
       </c>
       <c r="N438" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O438" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>0.09</v>
       </c>
       <c r="N439" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O439" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>0.09</v>
       </c>
       <c r="N440" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O440" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>0.09</v>
       </c>
       <c r="N441" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O441" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>0.09</v>
       </c>
       <c r="N442" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O442" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>0.09</v>
       </c>
       <c r="N444" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O444" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>0.09</v>
       </c>
       <c r="N445" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O445" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>0.09</v>
       </c>
       <c r="N446" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O446" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>0.09</v>
       </c>
       <c r="N448" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O448" t="inlineStr">
         <is>
